--- a/output/pdf_financials_xlsx/CNC.xlsx
+++ b/output/pdf_financials_xlsx/CNC.xlsx
@@ -757,19 +757,19 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>6.378103</v>
+        <v>-6.378103</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>7.692412</v>
+        <v>-3.377748</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>17.054811</v>
+        <v>-11.394943</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.951986</v>
+        <v>-5.483182</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>30.862685</v>
+        <v>-21.566653</v>
       </c>
     </row>
     <row r="17">
@@ -865,19 +865,19 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>6.378103</v>
+        <v>-6.378103</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>5.53508</v>
+        <v>-5.53508</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>14.224877</v>
+        <v>-14.224877</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.217584</v>
+        <v>-3.217584</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>26.214669</v>
+        <v>-26.214669</v>
       </c>
     </row>
     <row r="21">
@@ -931,19 +931,19 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>6.378103</v>
+        <v>-6.378103</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>5.53508</v>
+        <v>-5.53508</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>14.224877</v>
+        <v>-14.224877</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.217584</v>
+        <v>-3.217584</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>26.214669</v>
+        <v>-26.214669</v>
       </c>
     </row>
     <row r="24">
@@ -997,19 +997,19 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>79.726288</v>
+        <v>-79.726288</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>110.7016</v>
+        <v>-110.7016</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>129.317064</v>
+        <v>-129.317064</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>160.8792</v>
+        <v>-160.8792</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>201.6513</v>
+        <v>-201.6513</v>
       </c>
     </row>
     <row r="27">
@@ -1019,19 +1019,19 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>6.378103</v>
+        <v>-6.378103</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>7.692412</v>
+        <v>-3.377748</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>17.054811</v>
+        <v>-11.394943</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.951986</v>
+        <v>-5.483182</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>30.862685</v>
+        <v>-21.566653</v>
       </c>
     </row>
     <row r="28">
@@ -1063,19 +1063,19 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>6.378103</v>
+        <v>-6.378103</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>7.692412</v>
+        <v>-3.377748</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>17.054811</v>
+        <v>-11.394943</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.951986</v>
+        <v>-5.483182</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>30.862685</v>
+        <v>-21.566653</v>
       </c>
     </row>
     <row r="30">
@@ -1117,19 +1117,19 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>28.04493571067177</v>
+        <v>-63.86894463411716</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>16.59317127583531</v>
+        <v>-24.83499917463387</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>237.9864829944978</v>
+        <v>-41.31903701172057</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>15.06030988554625</v>
+        <v>-21.55186528016192</v>
       </c>
     </row>
     <row r="32">
@@ -3155,10 +3155,10 @@
         </is>
       </c>
       <c r="D118" s="3" t="n">
-        <v>0</v>
+        <v>-37.248538</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0</v>
+        <v>-56.671463</v>
       </c>
       <c r="F118" s="1" t="inlineStr">
         <is>
@@ -11474,19 +11474,19 @@
         </is>
       </c>
       <c r="E199" s="5" t="n">
-        <v>6.378103</v>
+        <v>-6.378103</v>
       </c>
       <c r="F199" s="5" t="n">
-        <v>5.53508</v>
+        <v>-5.53508</v>
       </c>
       <c r="G199" s="5" t="n">
-        <v>14.224877</v>
+        <v>-14.224877</v>
       </c>
       <c r="H199" s="5" t="n">
-        <v>3.217584</v>
+        <v>-3.217584</v>
       </c>
       <c r="I199" s="5" t="n">
-        <v>26.214669</v>
+        <v>-26.214669</v>
       </c>
     </row>
     <row r="200">

--- a/output/pdf_financials_xlsx/CNC.xlsx
+++ b/output/pdf_financials_xlsx/CNC.xlsx
@@ -675,13 +675,13 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.398414</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-1.091951</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.09748999999999999</v>
       </c>
     </row>
     <row r="13">
@@ -1025,13 +1025,13 @@
         <v>-3.377748</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-11.394943</v>
+        <v>-10.996529</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-5.483182</v>
+        <v>-4.391231</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-21.566653</v>
+        <v>-21.469163</v>
       </c>
     </row>
     <row r="28">
@@ -1069,13 +1069,13 @@
         <v>-3.377748</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-11.394943</v>
+        <v>-10.996529</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-5.483182</v>
+        <v>-4.391231</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-21.566653</v>
+        <v>-21.469163</v>
       </c>
     </row>
     <row r="30">
@@ -11238,7 +11238,7 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -11279,7 +11279,7 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -11829,7 +11829,7 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">

--- a/output/pdf_financials_xlsx/CNC.xlsx
+++ b/output/pdf_financials_xlsx/CNC.xlsx
@@ -2959,10 +2959,10 @@
         </is>
       </c>
       <c r="D111" s="3" t="n">
-        <v>0</v>
+        <v>-0.123574</v>
       </c>
       <c r="E111" s="3" t="n">
-        <v>0</v>
+        <v>-0.238794</v>
       </c>
       <c r="F111" s="1" t="inlineStr">
         <is>
@@ -3607,10 +3607,10 @@
         </is>
       </c>
       <c r="D134" s="3" t="n">
-        <v>0</v>
+        <v>-0.123574</v>
       </c>
       <c r="E134" s="3" t="n">
-        <v>0</v>
+        <v>-0.238794</v>
       </c>
       <c r="F134" s="1" t="inlineStr">
         <is>
@@ -3635,10 +3635,10 @@
         </is>
       </c>
       <c r="D135" s="3" t="n">
-        <v>-7.390795</v>
+        <v>-7.514369</v>
       </c>
       <c r="E135" s="3" t="n">
-        <v>-14.84043</v>
+        <v>-15.079224</v>
       </c>
       <c r="F135" s="1" t="inlineStr">
         <is>
